--- a/txt/bvd_card.xlsx
+++ b/txt/bvd_card.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giinhan/Downloads/bvd_0515/txt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13DA5964-E522-8446-8F2D-CA0F8E7D8ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FA119C-A17D-5549-9FD8-882C2808BDB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="2020" windowWidth="14560" windowHeight="17180" activeTab="4" xr2:uid="{8045F2DF-8EF6-BF4E-933D-991B0E7C2938}"/>
+    <workbookView xWindow="20860" yWindow="680" windowWidth="14560" windowHeight="17180" xr2:uid="{8045F2DF-8EF6-BF4E-933D-991B0E7C2938}"/>
   </bookViews>
   <sheets>
     <sheet name=" BVD" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Usac" sheetId="3" r:id="rId4"/>
     <sheet name="WORKS" sheetId="2" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="141">
   <si>
     <t>2026. 4. 12</t>
   </si>
@@ -385,6 +385,87 @@
   </si>
   <si>
     <t>w-04</t>
+  </si>
+  <si>
+    <t>f-07</t>
+  </si>
+  <si>
+    <t>f-08</t>
+  </si>
+  <si>
+    <t>f-09</t>
+  </si>
+  <si>
+    <t>f-10</t>
+  </si>
+  <si>
+    <t>f-11</t>
+  </si>
+  <si>
+    <t>f-12</t>
+  </si>
+  <si>
+    <t>f-13</t>
+  </si>
+  <si>
+    <t>f-14</t>
+  </si>
+  <si>
+    <t>f-15</t>
+  </si>
+  <si>
+    <t>f-16</t>
+  </si>
+  <si>
+    <t>f-17</t>
+  </si>
+  <si>
+    <t>2026. 5. 19</t>
+  </si>
+  <si>
+    <t>수박무꽃이 참 이쁘지만 꽃대가 이렇게 빠르게 올라오면 먹는 무로 자라지 못하므로 이 꽃으로는 한번 씨앗을 받아볼까요</t>
+  </si>
+  <si>
+    <t>얘도 심상치 않다…낮 기온이 높아지면 생기는 추대현상!!</t>
+  </si>
+  <si>
+    <t>열무가 쑥쑥 큽니다. 조만간 한번 솎아서 보내드리리</t>
+  </si>
+  <si>
+    <t>수미감자 4개 중 살아남은 튼실이 1</t>
+  </si>
+  <si>
+    <t>두백감자는 씨감자로 추가 심었더니 땅 뚫고 빼꼼</t>
+  </si>
+  <si>
+    <t>두백빼꼼 2</t>
+  </si>
+  <si>
+    <t>잘가 수미….</t>
+  </si>
+  <si>
+    <t>얘도 저 세상 갈듯 보였으나 회생하심</t>
+  </si>
+  <si>
+    <t>대만쪽파 너무 잘 크고요</t>
+  </si>
+  <si>
+    <t>베이비 쪽파, 베이비 잎상추</t>
+  </si>
+  <si>
+    <t>수박무 모종 사이에서 열심히 크고 있는 오이 둘</t>
+  </si>
+  <si>
+    <t>b-28</t>
+  </si>
+  <si>
+    <t>b-29</t>
+  </si>
+  <si>
+    <t>맘에드는 색상의 무당벌레 발견</t>
+  </si>
+  <si>
+    <t>전사장님에게 빌려드린 노지에서 옥시기들이 쑥쑥 자란다</t>
   </si>
 </sst>
 </file>
@@ -1086,10 +1167,26 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="2"/>
+      <c r="A29" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="2"/>
+      <c r="A30" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
@@ -1105,7 +1202,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC01D126-9DB7-EE44-A332-F0324C39CA9E}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="10.83203125" style="1"/>
@@ -1186,6 +1283,127 @@
       </c>
       <c r="C7" s="1" t="s">
         <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/txt/bvd_card.xlsx
+++ b/txt/bvd_card.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giinhan/Downloads/bvd_0515/txt/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giinhan/Downloads/_bvd_0515/txt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FA119C-A17D-5549-9FD8-882C2808BDB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFEBD5EE-A05E-9A45-9FE4-D621902CD2B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20860" yWindow="680" windowWidth="14560" windowHeight="17180" xr2:uid="{8045F2DF-8EF6-BF4E-933D-991B0E7C2938}"/>
+    <workbookView xWindow="19640" yWindow="680" windowWidth="14560" windowHeight="17180" activeTab="4" xr2:uid="{8045F2DF-8EF6-BF4E-933D-991B0E7C2938}"/>
   </bookViews>
   <sheets>
     <sheet name=" BVD" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="240">
   <si>
     <t>2026. 4. 12</t>
   </si>
@@ -466,13 +466,310 @@
   </si>
   <si>
     <t>전사장님에게 빌려드린 노지에서 옥시기들이 쑥쑥 자란다</t>
+  </si>
+  <si>
+    <t>w-05-0522</t>
+  </si>
+  <si>
+    <t>w-06-0522</t>
+  </si>
+  <si>
+    <t>w-07-0522</t>
+  </si>
+  <si>
+    <t>w-08-0522</t>
+  </si>
+  <si>
+    <t>w-09-0522</t>
+  </si>
+  <si>
+    <t>w-10-0522</t>
+  </si>
+  <si>
+    <t>w-11-0522</t>
+  </si>
+  <si>
+    <t>2026. 5. 22</t>
+  </si>
+  <si>
+    <t>새우랑 빠빠빠빠껀가요</t>
+  </si>
+  <si>
+    <t>여주를 심었습니다. 덩굴같이 자랄테니까 타고올라갈 줄을 달아줄게요</t>
+  </si>
+  <si>
+    <t>햇빛이 강해서 축 늘어진 것이 애처로워 보이지만 호박은 생명력이 강합니다. 아주 울창해질꺼야. 고 앞에는 샐러리 삼총사, 고 앞에 보라색은 비트</t>
+  </si>
+  <si>
+    <t>완두콩이 전멸해서 토마토를 심어보았습니다</t>
+  </si>
+  <si>
+    <t>뭐 바질은 뭐. 어여 쑥쑥 커라.</t>
+  </si>
+  <si>
+    <t>브로컬리니~ 맛있겠다~</t>
+  </si>
+  <si>
+    <t>u-09-0522</t>
+  </si>
+  <si>
+    <t>u-10-0522</t>
+  </si>
+  <si>
+    <t>u-11-0522</t>
+  </si>
+  <si>
+    <t>u-12-0522</t>
+  </si>
+  <si>
+    <t>u-13-0522</t>
+  </si>
+  <si>
+    <t>u-14-0522</t>
+  </si>
+  <si>
+    <t>u-15-0522</t>
+  </si>
+  <si>
+    <t>u-16-0522</t>
+  </si>
+  <si>
+    <t>u-17-0522</t>
+  </si>
+  <si>
+    <t>u-18-0522</t>
+  </si>
+  <si>
+    <t>u-19-0522</t>
+  </si>
+  <si>
+    <t>u-20-0522</t>
+  </si>
+  <si>
+    <t>u-21-0522</t>
+  </si>
+  <si>
+    <t>u-22-0522</t>
+  </si>
+  <si>
+    <t>블루베리 No.1</t>
+  </si>
+  <si>
+    <t>블루베리 전용 비료를 뿌립니다.</t>
+  </si>
+  <si>
+    <t>No.1의 No.1이 보입니당</t>
+  </si>
+  <si>
+    <t>블루베리 No.2 측면</t>
+  </si>
+  <si>
+    <t>블루베리 No.2 정면 (비닐하우스 메인 고랑 기준)</t>
+  </si>
+  <si>
+    <t>루꼴라들이 힘겹게 살아남았슴다!</t>
+  </si>
+  <si>
+    <t>당귀는 전멸하여 다시 사다 심음…애돌아 이번엔 반드시</t>
+  </si>
+  <si>
+    <t>잎채소(상추류)들이 조금씩 올라오는 현장 -힘내자</t>
+  </si>
+  <si>
+    <t>해가 너무 강했던 지난 몇주동안 청양고추도 시들해서 절반은 다시 심었어요!</t>
+  </si>
+  <si>
+    <t>같이 심었는데 누구는 작고 누구는 큰건 사람이나 동물이나 식물이나 다 있는 일인가봅니다</t>
+  </si>
+  <si>
+    <t>노지 고구마 한줄 길게 심어 놨어요 그중에 하나</t>
+  </si>
+  <si>
+    <t>그중에 둘</t>
+  </si>
+  <si>
+    <t>그중에 셋 (그리고 또 매니매니 더 있답니다)</t>
+  </si>
+  <si>
+    <t>감자싹 나와라 화이팅하고 있고! 추가 써있는 곳에 모종으로 키운 녀석들 옮겨심을 예정이에요! 운명하신 들깨는 비버댐 스페어로 심은 곳의 것으로 대체할 예정입니닷!</t>
+  </si>
+  <si>
+    <t>s-04-0522</t>
+  </si>
+  <si>
+    <t>s-05-0522</t>
+  </si>
+  <si>
+    <t>s-06-0522</t>
+  </si>
+  <si>
+    <t>s-07-0522</t>
+  </si>
+  <si>
+    <t>s-08-0522</t>
+  </si>
+  <si>
+    <t>s-09-0522</t>
+  </si>
+  <si>
+    <t>s-10-0522</t>
+  </si>
+  <si>
+    <t>s-11-0522</t>
+  </si>
+  <si>
+    <t>s-12-0522</t>
+  </si>
+  <si>
+    <t>s-13-0522</t>
+  </si>
+  <si>
+    <t>s-14-0522</t>
+  </si>
+  <si>
+    <t>s-15-0522</t>
+  </si>
+  <si>
+    <t>s-16-0522</t>
+  </si>
+  <si>
+    <t>s-17-0522</t>
+  </si>
+  <si>
+    <t>s-18-0522</t>
+  </si>
+  <si>
+    <t>s-19-0522</t>
+  </si>
+  <si>
+    <t>s-20-0522</t>
+  </si>
+  <si>
+    <t>s-21-0522</t>
+  </si>
+  <si>
+    <t>가지 1 쑥쑥 커요</t>
+  </si>
+  <si>
+    <t>가지 2 사이드뷰</t>
+  </si>
+  <si>
+    <t>가지 2 탑뷰</t>
+  </si>
+  <si>
+    <t>가지 1 탑뷰 이쁘쥬</t>
+  </si>
+  <si>
+    <t>파프리카님</t>
+  </si>
+  <si>
+    <t>파프리카님 한번더</t>
+  </si>
+  <si>
+    <t>도마도 아직 작은 녀석</t>
+  </si>
+  <si>
+    <t>도마도 중간 녀석</t>
+  </si>
+  <si>
+    <t>도마도 젤 큰애</t>
+  </si>
+  <si>
+    <t>도마도 순을 정리해주고 첫 꽃들을 따주었습니다. 맘약해지면 안됨</t>
+  </si>
+  <si>
+    <t>루꼴라</t>
+  </si>
+  <si>
+    <t>혼자만 갑자기 크게 자란 루꼴라. 정말 농사는 모를 일이다.</t>
+  </si>
+  <si>
+    <t>부추 2…...........영…</t>
+  </si>
+  <si>
+    <t>부추 1….......영….</t>
+  </si>
+  <si>
+    <t>오이 둘이서 아주 쌩썡하게 잘 자라고 있슴다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">단호박 독야청청 </t>
+  </si>
+  <si>
+    <t>단호박 미니잎들 올라오는 귀여운 광경</t>
+  </si>
+  <si>
+    <t>밭뷰 : 씨앗자리에 직파한 씨앗들이 힘내서 올라오기를 기다리고 있습니다.</t>
+  </si>
+  <si>
+    <t>f-18-0522</t>
+  </si>
+  <si>
+    <t>f-19-0522</t>
+  </si>
+  <si>
+    <t>토마토 순을 정리해주면서 일찍 핀 꽃에서 난 쪼꼬미 열매를 따드렸습니다. 바이바이….</t>
+  </si>
+  <si>
+    <t>운명하센 바질만 한번 리필해드리고! 곧 열무 한번 솎아줘야겠음!</t>
+  </si>
+  <si>
+    <t>b-30-0522</t>
+  </si>
+  <si>
+    <t>b-31-0522</t>
+  </si>
+  <si>
+    <t>b-32-0522</t>
+  </si>
+  <si>
+    <t>b-33-0522</t>
+  </si>
+  <si>
+    <t>b-34-0522</t>
+  </si>
+  <si>
+    <t>b-35-0522</t>
+  </si>
+  <si>
+    <t>b-36-0522</t>
+  </si>
+  <si>
+    <t>b-37-0522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">여기도 저기도 여기저기 </t>
+  </si>
+  <si>
+    <t>혹시 모를 사태에 대비하여 모든 모종의 여분을 준비해놓았다 하하하</t>
+  </si>
+  <si>
+    <t>S팀 부추들이 시들시들하여…노지에 부추씨앗을 열심히 뿌려놨지래</t>
+  </si>
+  <si>
+    <t>나눔씨앗 분으로 안내했던 잎채소들 노지에서 쑥쑥</t>
+  </si>
+  <si>
+    <t>미나리숲에 오신걸 환영합니다</t>
+  </si>
+  <si>
+    <t>하우스의 잎들깨는 심는 족족 다 죽고…노지는 살아나고 아 어렵다 농사</t>
+  </si>
+  <si>
+    <t>몇년째 땅 속에서 부활을 반복중인 우리 기특한 딜즈</t>
+  </si>
+  <si>
+    <t>씨앗으로 시작한 애들 모종판에서 아직 애지중지</t>
+  </si>
+  <si>
+    <t>전체 밭뷰이옵니다..감자 좀 올라오지??? 이제 좀???</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -489,6 +786,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -514,10 +818,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -852,7 +1157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9333401-F013-1F47-ABF0-251B841A167D}">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="10.83203125" style="1"/>
@@ -1189,10 +1494,92 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="2"/>
+      <c r="A31" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="2"/>
+      <c r="A32" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>238</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1202,7 +1589,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC01D126-9DB7-EE44-A332-F0324C39CA9E}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="10.83203125" style="1"/>
@@ -1406,6 +1793,28 @@
         <v>136</v>
       </c>
     </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1414,7 +1823,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF858591-3711-5640-84D0-12D568B8E09C}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="10.83203125" style="1"/>
@@ -1464,6 +1873,204 @@
         <v>110</v>
       </c>
     </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1472,7 +2079,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C095EB-359B-7045-8624-9E27F258E220}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -1580,6 +2187,160 @@
         <v>110</v>
       </c>
     </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1588,7 +2349,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53020BC4-5661-9949-9AB8-897A43F05863}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="10.83203125" style="1"/>
@@ -1649,6 +2410,83 @@
         <v>110</v>
       </c>
     </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/txt/bvd_card.xlsx
+++ b/txt/bvd_card.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giinhan/Downloads/_bvd_0515/txt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFEBD5EE-A05E-9A45-9FE4-D621902CD2B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A761380-23AE-DB4C-A064-AD965E681F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19640" yWindow="680" windowWidth="14560" windowHeight="17180" activeTab="4" xr2:uid="{8045F2DF-8EF6-BF4E-933D-991B0E7C2938}"/>
+    <workbookView xWindow="19640" yWindow="680" windowWidth="14560" windowHeight="17180" activeTab="3" xr2:uid="{8045F2DF-8EF6-BF4E-933D-991B0E7C2938}"/>
   </bookViews>
   <sheets>
     <sheet name=" BVD" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="242">
   <si>
     <t>2026. 4. 12</t>
   </si>
@@ -763,6 +763,12 @@
   </si>
   <si>
     <t>전체 밭뷰이옵니다..감자 좀 올라오지??? 이제 좀???</t>
+  </si>
+  <si>
+    <t>"미나리 전멸"</t>
+  </si>
+  <si>
+    <t>u-23-0515-1/2</t>
   </si>
 </sst>
 </file>
@@ -2079,7 +2085,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C095EB-359B-7045-8624-9E27F258E220}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -2339,6 +2345,17 @@
       </c>
       <c r="C23" s="1" t="s">
         <v>182</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/txt/bvd_card.xlsx
+++ b/txt/bvd_card.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giinhan/Downloads/_bvd_0515/txt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A761380-23AE-DB4C-A064-AD965E681F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AB67E1-8D6F-FC43-8C4A-BD9773F0836E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19640" yWindow="680" windowWidth="14560" windowHeight="17180" activeTab="3" xr2:uid="{8045F2DF-8EF6-BF4E-933D-991B0E7C2938}"/>
+    <workbookView xWindow="19640" yWindow="680" windowWidth="14560" windowHeight="17180" activeTab="1" xr2:uid="{8045F2DF-8EF6-BF4E-933D-991B0E7C2938}"/>
   </bookViews>
   <sheets>
     <sheet name=" BVD" sheetId="1" r:id="rId1"/>
@@ -711,9 +711,6 @@
     <t>토마토 순을 정리해주면서 일찍 핀 꽃에서 난 쪼꼬미 열매를 따드렸습니다. 바이바이….</t>
   </si>
   <si>
-    <t>운명하센 바질만 한번 리필해드리고! 곧 열무 한번 솎아줘야겠음!</t>
-  </si>
-  <si>
     <t>b-30-0522</t>
   </si>
   <si>
@@ -769,6 +766,9 @@
   </si>
   <si>
     <t>u-23-0515-1/2</t>
+  </si>
+  <si>
+    <t>운명하신 바질만 한번 리필해드리고! 곧 열무 한번 솎아줘야겠음!</t>
   </si>
 </sst>
 </file>
@@ -1501,90 +1501,90 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -1818,7 +1818,7 @@
         <v>148</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -2349,13 +2349,13 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -2501,7 +2501,7 @@
         <v>148</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/txt/bvd_card.xlsx
+++ b/txt/bvd_card.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giinhan/Downloads/_bvd_0515/txt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AB67E1-8D6F-FC43-8C4A-BD9773F0836E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BAC52E0-7937-DC4F-96B5-70940BF0F74C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19640" yWindow="680" windowWidth="14560" windowHeight="17180" activeTab="1" xr2:uid="{8045F2DF-8EF6-BF4E-933D-991B0E7C2938}"/>
+    <workbookView xWindow="19640" yWindow="680" windowWidth="14560" windowHeight="17180" activeTab="4" xr2:uid="{8045F2DF-8EF6-BF4E-933D-991B0E7C2938}"/>
   </bookViews>
   <sheets>
     <sheet name=" BVD" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="285">
   <si>
     <t>2026. 4. 12</t>
   </si>
@@ -769,6 +769,135 @@
   </si>
   <si>
     <t>운명하신 바질만 한번 리필해드리고! 곧 열무 한번 솎아줘야겠음!</t>
+  </si>
+  <si>
+    <t>0602-b-38</t>
+  </si>
+  <si>
+    <t>2026. 6. 2</t>
+  </si>
+  <si>
+    <t>상추랑 시금치</t>
+  </si>
+  <si>
+    <t>0602-b-39</t>
+  </si>
+  <si>
+    <t>청경채</t>
+  </si>
+  <si>
+    <t>오크상추라 부르는</t>
+  </si>
+  <si>
+    <t>미니밭에 뒤늦게 뿌렸던 잎채소 믹스</t>
+  </si>
+  <si>
+    <t>0602-b-40</t>
+  </si>
+  <si>
+    <t>0602-b-41</t>
+  </si>
+  <si>
+    <t>0602-b-42</t>
+  </si>
+  <si>
+    <t>너넨 누구니</t>
+  </si>
+  <si>
+    <t>0602-f-20</t>
+  </si>
+  <si>
+    <t>밭뷰</t>
+  </si>
+  <si>
+    <t>0602-f-21</t>
+  </si>
+  <si>
+    <t>쪽파뷰</t>
+  </si>
+  <si>
+    <t>미니쪽파뷰</t>
+  </si>
+  <si>
+    <t xml:space="preserve">두백감자 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">수미감자 </t>
+  </si>
+  <si>
+    <t>자…열무를 솎아서 보내드리고 싶습니다!</t>
+  </si>
+  <si>
+    <t>0602-f-22</t>
+  </si>
+  <si>
+    <t>0602-f-23</t>
+  </si>
+  <si>
+    <t>0602-f-24</t>
+  </si>
+  <si>
+    <t>0602-f-25</t>
+  </si>
+  <si>
+    <t>0602-s-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">밭뷰  </t>
+  </si>
+  <si>
+    <t>키큰 토마토와 키작은 토마토</t>
+  </si>
+  <si>
+    <t>그..루꼴라 보내드릴게요</t>
+  </si>
+  <si>
+    <t>0602-s-23</t>
+  </si>
+  <si>
+    <t>0602-s-24</t>
+  </si>
+  <si>
+    <t>0602-s-25</t>
+  </si>
+  <si>
+    <t>0602-s-26</t>
+  </si>
+  <si>
+    <t>0602-s-27</t>
+  </si>
+  <si>
+    <t>0602-s-28</t>
+  </si>
+  <si>
+    <t>0602-s-29</t>
+  </si>
+  <si>
+    <t>오이구요</t>
+  </si>
+  <si>
+    <t>가지가 그새 이만큼이나 컸어요 지난주에 귀여웠는뎅 청소년대따</t>
+  </si>
+  <si>
+    <t>파프리카뷰</t>
+  </si>
+  <si>
+    <t>제가 없는 일주일사이에 한동수님이 맘대로 적양배추를 추가하셨습니다…ㅋㅋ 이렇게 됨..늘이래…증정!!</t>
+  </si>
+  <si>
+    <t>호박이에요 (벌써부터 삐져나가기 시작)(나중에 난리남)(호박만의 세상이 됨)</t>
+  </si>
+  <si>
+    <t>0602-w-12</t>
+  </si>
+  <si>
+    <t>큰거 맞나..암튼 죽지는 않았슴</t>
+  </si>
+  <si>
+    <t>0602-w-13</t>
+  </si>
+  <si>
+    <t>걍 귀여운 탑뷰</t>
   </si>
 </sst>
 </file>
@@ -1163,7 +1292,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9333401-F013-1F47-ABF0-251B841A167D}">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="10.83203125" style="1"/>
@@ -1587,6 +1716,61 @@
         <v>237</v>
       </c>
     </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1595,7 +1779,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC01D126-9DB7-EE44-A332-F0324C39CA9E}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="10.83203125" style="1"/>
@@ -1821,6 +2005,72 @@
         <v>241</v>
       </c>
     </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1829,7 +2079,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF858591-3711-5640-84D0-12D568B8E09C}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="10.83203125" style="1"/>
@@ -2075,6 +2325,94 @@
       </c>
       <c r="C22" s="1" t="s">
         <v>218</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -2366,7 +2704,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53020BC4-5661-9949-9AB8-897A43F05863}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="10.83203125" style="1"/>
@@ -2504,6 +2842,28 @@
         <v>238</v>
       </c>
     </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/txt/bvd_card.xlsx
+++ b/txt/bvd_card.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giinhan/Downloads/_bvd_0515/txt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BAC52E0-7937-DC4F-96B5-70940BF0F74C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0AC4811-2FA0-D549-8713-63B92DEB759B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19640" yWindow="680" windowWidth="14560" windowHeight="17180" activeTab="4" xr2:uid="{8045F2DF-8EF6-BF4E-933D-991B0E7C2938}"/>
+    <workbookView xWindow="19640" yWindow="680" windowWidth="14560" windowHeight="17180" xr2:uid="{8045F2DF-8EF6-BF4E-933D-991B0E7C2938}"/>
   </bookViews>
   <sheets>
     <sheet name=" BVD" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="328">
   <si>
     <t>2026. 4. 12</t>
   </si>
@@ -898,6 +898,135 @@
   </si>
   <si>
     <t>걍 귀여운 탑뷰</t>
+  </si>
+  <si>
+    <t>0603-w-14</t>
+  </si>
+  <si>
+    <t>2026. 6. 3</t>
+  </si>
+  <si>
+    <t>하루지나고 보니 더 큰거 같아서 찍어봄</t>
+  </si>
+  <si>
+    <t>나만 그런가..뒤돌아서면 애들이 계속 크는거 같아</t>
+  </si>
+  <si>
+    <t>호박은 옆집 괴롭히지 말라고 교통정리해드리규</t>
+  </si>
+  <si>
+    <t>0603-w-15</t>
+  </si>
+  <si>
+    <t>0603-w-16</t>
+  </si>
+  <si>
+    <t>0603-w-17</t>
+  </si>
+  <si>
+    <t>0603-u-24</t>
+  </si>
+  <si>
+    <t>0603-u-25</t>
+  </si>
+  <si>
+    <t>0603-u-26</t>
+  </si>
+  <si>
+    <t>0603-u-27</t>
+  </si>
+  <si>
+    <t>0603-u-28</t>
+  </si>
+  <si>
+    <t>여기부터 저기까지 다 고구마</t>
+  </si>
+  <si>
+    <t>뒤돌아서 또 여기부터 저기까지 다 고구마</t>
+  </si>
+  <si>
+    <t>그…다른 밭보다 왜 유난히 잘 안되지….만 결국엔 승리할것입니다 (다짐)</t>
+  </si>
+  <si>
+    <t>일단 블루베리가 있는 밭이라고</t>
+  </si>
+  <si>
+    <t>불황 와중에 살아남은 애들이 기특한…계속 힘써봅니다</t>
+  </si>
+  <si>
+    <t>여주 기둥 세워드림</t>
+  </si>
+  <si>
+    <t>0603-b-43</t>
+  </si>
+  <si>
+    <t>0603-b-44</t>
+  </si>
+  <si>
+    <t>0603-b-45</t>
+  </si>
+  <si>
+    <t>0603-b-46</t>
+  </si>
+  <si>
+    <t>0603-b-47</t>
+  </si>
+  <si>
+    <t>0603-b-48</t>
+  </si>
+  <si>
+    <t>0603-b-49</t>
+  </si>
+  <si>
+    <t>0603-b-50</t>
+  </si>
+  <si>
+    <t>0603-b-51</t>
+  </si>
+  <si>
+    <t>0603-b-52</t>
+  </si>
+  <si>
+    <t>0603-b-53</t>
+  </si>
+  <si>
+    <t>0603-b-54</t>
+  </si>
+  <si>
+    <t>모종을 계속 키우고 있어요 타이밍 안끊어지게</t>
+  </si>
+  <si>
+    <t>자연에서 귀한 색</t>
+  </si>
+  <si>
+    <t>남색초원하늘소. 더듬이거 너무너무너무 멋져부러</t>
+  </si>
+  <si>
+    <t>얘가 뭐였더라…모종 잎이 두종류라 신기하다고 그랬었는데</t>
+  </si>
+  <si>
+    <t>유난히 혼자 잘크는애들 기둥 세워드림</t>
+  </si>
+  <si>
+    <t>저뒤에 메리골드 씨앗 심었는데…..기미도 안보여</t>
+  </si>
+  <si>
+    <t>이렇게 잘 크는 애들도 있는데 정말 알수없다</t>
+  </si>
+  <si>
+    <t>이러케 아무런 신호도 없을 수도 있다. (씨앗 왕창 심음)</t>
+  </si>
+  <si>
+    <t>여기도 마니 심어놨는데</t>
+  </si>
+  <si>
+    <t>기별없는 땅이 너무 많다 ㅋㅋ 아악</t>
+  </si>
+  <si>
+    <t>여긴 또 반반이여 반만 자라고 반은 소식없음</t>
+  </si>
+  <si>
+    <t>휴…힘내보자 더 신경써보마</t>
   </si>
 </sst>
 </file>
@@ -1292,7 +1421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9333401-F013-1F47-ABF0-251B841A167D}">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="10.83203125" style="1"/>
@@ -1769,6 +1898,138 @@
       </c>
       <c r="C43" s="1" t="s">
         <v>248</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -2423,7 +2684,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C095EB-359B-7045-8624-9E27F258E220}">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -2696,6 +2957,61 @@
         <v>239</v>
       </c>
     </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2704,7 +3020,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53020BC4-5661-9949-9AB8-897A43F05863}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="10.83203125" style="1"/>
@@ -2864,6 +3180,50 @@
         <v>284</v>
       </c>
     </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
